--- a/AtchisonRegime/Outputs/Japan/df_regInflation_Japan.xlsx
+++ b/AtchisonRegime/Outputs/Japan/df_regInflation_Japan.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H617"/>
+  <dimension ref="A1:H618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16471,24 +16471,50 @@
         <v>45747</v>
       </c>
       <c r="B617" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="C617" t="n">
-        <v>3.800000000000001</v>
+        <v>3.766666666666667</v>
       </c>
       <c r="D617" t="n">
-        <v>3.077777777777778</v>
+        <v>3.075</v>
       </c>
       <c r="E617" t="n">
-        <v>0.5286700894623437</v>
+        <v>0.5255609248358792</v>
       </c>
       <c r="F617" t="b">
         <v>1</v>
       </c>
       <c r="G617" t="n">
-        <v>1.366111373837551</v>
+        <v>1.316054207954405</v>
       </c>
       <c r="H617" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B618" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C618" t="n">
+        <v>3.633333333333334</v>
+      </c>
+      <c r="D618" t="n">
+        <v>3.105555555555556</v>
+      </c>
+      <c r="E618" t="n">
+        <v>0.5231467668662387</v>
+      </c>
+      <c r="F618" t="b">
+        <v>1</v>
+      </c>
+      <c r="G618" t="n">
+        <v>1.008852221221361</v>
+      </c>
+      <c r="H618" t="b">
         <v>1</v>
       </c>
     </row>
